--- a/Excel Sheets Practice/All Practice Next.xlsx
+++ b/Excel Sheets Practice/All Practice Next.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cadd Mentor\Student_Class_Code\Dhruv Python Classes\Dhruv Excel Sheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cadd Mentor\Student_Class_Code\Dhruv Python Classes\Excel Sheets Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09DECAB-9AE1-4E86-AF17-0D95205E59FB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB993C9B-CB00-4256-8D32-F12F6652172F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Practice Date Formule" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="9" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -916,7 +916,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4C4AEEFD-C8F7-4759-ACC5-DBCF80DC5D05}" name="PivotTable1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4C4AEEFD-C8F7-4759-ACC5-DBCF80DC5D05}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:C7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0">
@@ -1373,11 +1373,11 @@
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <f ca="1">TODAY()</f>
-        <v>46043</v>
+        <v>46121</v>
       </c>
       <c r="B2" s="3">
         <f ca="1">NOW()</f>
-        <v>46043.770485763889</v>
+        <v>46121.765954629627</v>
       </c>
       <c r="C2">
         <f ca="1">YEAR(B2)</f>
@@ -1385,11 +1385,11 @@
       </c>
       <c r="D2">
         <f ca="1">MONTH(B2)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <f ca="1">DAY(B2)</f>
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F2">
         <f ca="1">HOUR(B2)</f>
@@ -1397,21 +1397,21 @@
       </c>
       <c r="G2">
         <f ca="1">MINUTE(B2)</f>
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="H2">
         <f ca="1">SECOND(B2)</f>
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="I2" s="3">
         <f ca="1">EDATE(A2,4)</f>
-        <v>46163</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="I4" s="2">
         <f ca="1">EDATE(A2,3*12)</f>
-        <v>47139</v>
+        <v>47217</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
